--- a/セリフ編集/その他セリフ/17-関係性フラグ.xlsx
+++ b/セリフ編集/その他セリフ/17-関係性フラグ.xlsx
@@ -800,7 +800,7 @@
     <row r="19" ht="40" customHeight="1">
       <c r="A19" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FLAG_DIALOGUE.M-1.normal[1]</t>
+          <t xml:space="preserve">FLAG_DIALOGUE.M-1.standard[1]</t>
         </is>
       </c>
       <c r="B19" t="inlineStr" s="2">
@@ -815,12 +815,12 @@
       </c>
       <c r="D19" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">M-1.normal[1]</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">M-1.standard[1]</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G19" t="inlineStr" s="3">
@@ -832,7 +832,7 @@
     <row r="20" ht="40" customHeight="1">
       <c r="A20" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FLAG_DIALOGUE.M-1.normal[2]</t>
+          <t xml:space="preserve">FLAG_DIALOGUE.M-1.standard[2]</t>
         </is>
       </c>
       <c r="B20" t="inlineStr" s="2">
@@ -847,12 +847,12 @@
       </c>
       <c r="D20" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">M-1.normal[2]</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">M-1.standard[2]</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G20" t="inlineStr" s="3">
@@ -864,7 +864,7 @@
     <row r="21" ht="40" customHeight="1">
       <c r="A21" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FLAG_DIALOGUE.M-1.normal[3]</t>
+          <t xml:space="preserve">FLAG_DIALOGUE.M-1.standard[3]</t>
         </is>
       </c>
       <c r="B21" t="inlineStr" s="2">
@@ -879,12 +879,12 @@
       </c>
       <c r="D21" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">M-1.normal[3]</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">M-1.standard[3]</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G21" t="inlineStr" s="3">
@@ -1472,7 +1472,7 @@
     <row r="40" ht="40" customHeight="1">
       <c r="A40" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FLAG_DIALOGUE.M-2.normal[1]</t>
+          <t xml:space="preserve">FLAG_DIALOGUE.M-2.standard[1]</t>
         </is>
       </c>
       <c r="B40" t="inlineStr" s="2">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="D40" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">M-2.normal[1]</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">M-2.standard[1]</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G40" t="inlineStr" s="3">
@@ -1504,7 +1504,7 @@
     <row r="41" ht="40" customHeight="1">
       <c r="A41" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FLAG_DIALOGUE.M-2.normal[2]</t>
+          <t xml:space="preserve">FLAG_DIALOGUE.M-2.standard[2]</t>
         </is>
       </c>
       <c r="B41" t="inlineStr" s="2">
@@ -1519,12 +1519,12 @@
       </c>
       <c r="D41" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">M-2.normal[2]</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">M-2.standard[2]</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G41" t="inlineStr" s="3">
@@ -1536,7 +1536,7 @@
     <row r="42" ht="40" customHeight="1">
       <c r="A42" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FLAG_DIALOGUE.M-2.normal[3]</t>
+          <t xml:space="preserve">FLAG_DIALOGUE.M-2.standard[3]</t>
         </is>
       </c>
       <c r="B42" t="inlineStr" s="2">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="D42" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">M-2.normal[3]</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">M-2.standard[3]</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G42" t="inlineStr" s="3">
@@ -2144,7 +2144,7 @@
     <row r="61" ht="40" customHeight="1">
       <c r="A61" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FLAG_DIALOGUE.M-3.normal[1]</t>
+          <t xml:space="preserve">FLAG_DIALOGUE.M-3.standard[1]</t>
         </is>
       </c>
       <c r="B61" t="inlineStr" s="2">
@@ -2159,12 +2159,12 @@
       </c>
       <c r="D61" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">M-3.normal[1]</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">M-3.standard[1]</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G61" t="inlineStr" s="3">
@@ -2176,7 +2176,7 @@
     <row r="62" ht="40" customHeight="1">
       <c r="A62" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FLAG_DIALOGUE.M-3.normal[2]</t>
+          <t xml:space="preserve">FLAG_DIALOGUE.M-3.standard[2]</t>
         </is>
       </c>
       <c r="B62" t="inlineStr" s="2">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="D62" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">M-3.normal[2]</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">M-3.standard[2]</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G62" t="inlineStr" s="3">
@@ -2208,7 +2208,7 @@
     <row r="63" ht="40" customHeight="1">
       <c r="A63" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FLAG_DIALOGUE.M-3.normal[3]</t>
+          <t xml:space="preserve">FLAG_DIALOGUE.M-3.standard[3]</t>
         </is>
       </c>
       <c r="B63" t="inlineStr" s="2">
@@ -2223,12 +2223,12 @@
       </c>
       <c r="D63" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">M-3.normal[3]</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">M-3.standard[3]</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G63" t="inlineStr" s="3">
@@ -2784,7 +2784,7 @@
     <row r="81" ht="40" customHeight="1">
       <c r="A81" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FLAG_DIALOGUE.M-4.normal[1]</t>
+          <t xml:space="preserve">FLAG_DIALOGUE.M-4.standard[1]</t>
         </is>
       </c>
       <c r="B81" t="inlineStr" s="2">
@@ -2799,12 +2799,12 @@
       </c>
       <c r="D81" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">M-4.normal[1]</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">M-4.standard[1]</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G81" t="inlineStr" s="3">
@@ -2816,7 +2816,7 @@
     <row r="82" ht="40" customHeight="1">
       <c r="A82" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FLAG_DIALOGUE.M-4.normal[2]</t>
+          <t xml:space="preserve">FLAG_DIALOGUE.M-4.standard[2]</t>
         </is>
       </c>
       <c r="B82" t="inlineStr" s="2">
@@ -2831,12 +2831,12 @@
       </c>
       <c r="D82" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">M-4.normal[2]</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">M-4.standard[2]</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G82" t="inlineStr" s="3">
@@ -2848,7 +2848,7 @@
     <row r="83" ht="40" customHeight="1">
       <c r="A83" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FLAG_DIALOGUE.M-4.normal[3]</t>
+          <t xml:space="preserve">FLAG_DIALOGUE.M-4.standard[3]</t>
         </is>
       </c>
       <c r="B83" t="inlineStr" s="2">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="D83" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">M-4.normal[3]</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">M-4.standard[3]</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G83" t="inlineStr" s="3">
@@ -3456,7 +3456,7 @@
     <row r="102" ht="40" customHeight="1">
       <c r="A102" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FLAG_DIALOGUE.M-5.normal[1]</t>
+          <t xml:space="preserve">FLAG_DIALOGUE.M-5.standard[1]</t>
         </is>
       </c>
       <c r="B102" t="inlineStr" s="2">
@@ -3471,12 +3471,12 @@
       </c>
       <c r="D102" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">M-5.normal[1]</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">M-5.standard[1]</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G102" t="inlineStr" s="3">
@@ -3488,7 +3488,7 @@
     <row r="103" ht="40" customHeight="1">
       <c r="A103" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FLAG_DIALOGUE.M-5.normal[2]</t>
+          <t xml:space="preserve">FLAG_DIALOGUE.M-5.standard[2]</t>
         </is>
       </c>
       <c r="B103" t="inlineStr" s="2">
@@ -3503,12 +3503,12 @@
       </c>
       <c r="D103" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">M-5.normal[2]</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">M-5.standard[2]</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G103" t="inlineStr" s="3">
@@ -3520,7 +3520,7 @@
     <row r="104" ht="40" customHeight="1">
       <c r="A104" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FLAG_DIALOGUE.M-5.normal[3]</t>
+          <t xml:space="preserve">FLAG_DIALOGUE.M-5.standard[3]</t>
         </is>
       </c>
       <c r="B104" t="inlineStr" s="2">
@@ -3535,12 +3535,12 @@
       </c>
       <c r="D104" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">M-5.normal[3]</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">M-5.standard[3]</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G104" t="inlineStr" s="3">
@@ -4128,7 +4128,7 @@
     <row r="123" ht="40" customHeight="1">
       <c r="A123" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FLAG_DIALOGUE.M-6.normal[1]</t>
+          <t xml:space="preserve">FLAG_DIALOGUE.M-6.standard[1]</t>
         </is>
       </c>
       <c r="B123" t="inlineStr" s="2">
@@ -4143,12 +4143,12 @@
       </c>
       <c r="D123" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">M-6.normal[1]</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">M-6.standard[1]</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G123" t="inlineStr" s="3">
@@ -4160,7 +4160,7 @@
     <row r="124" ht="40" customHeight="1">
       <c r="A124" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FLAG_DIALOGUE.M-6.normal[2]</t>
+          <t xml:space="preserve">FLAG_DIALOGUE.M-6.standard[2]</t>
         </is>
       </c>
       <c r="B124" t="inlineStr" s="2">
@@ -4175,12 +4175,12 @@
       </c>
       <c r="D124" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">M-6.normal[2]</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">M-6.standard[2]</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G124" t="inlineStr" s="3">
@@ -4192,7 +4192,7 @@
     <row r="125" ht="40" customHeight="1">
       <c r="A125" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FLAG_DIALOGUE.M-6.normal[3]</t>
+          <t xml:space="preserve">FLAG_DIALOGUE.M-6.standard[3]</t>
         </is>
       </c>
       <c r="B125" t="inlineStr" s="2">
@@ -4207,12 +4207,12 @@
       </c>
       <c r="D125" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">M-6.normal[3]</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">M-6.standard[3]</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G125" t="inlineStr" s="3">
@@ -4800,7 +4800,7 @@
     <row r="144" ht="40" customHeight="1">
       <c r="A144" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FLAG_DIALOGUE.M-7.normal[1]</t>
+          <t xml:space="preserve">FLAG_DIALOGUE.M-7.standard[1]</t>
         </is>
       </c>
       <c r="B144" t="inlineStr" s="2">
@@ -4815,12 +4815,12 @@
       </c>
       <c r="D144" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">M-7.normal[1]</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">M-7.standard[1]</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G144" t="inlineStr" s="3">
@@ -4832,7 +4832,7 @@
     <row r="145" ht="40" customHeight="1">
       <c r="A145" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FLAG_DIALOGUE.M-7.normal[2]</t>
+          <t xml:space="preserve">FLAG_DIALOGUE.M-7.standard[2]</t>
         </is>
       </c>
       <c r="B145" t="inlineStr" s="2">
@@ -4847,12 +4847,12 @@
       </c>
       <c r="D145" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">M-7.normal[2]</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">M-7.standard[2]</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G145" t="inlineStr" s="3">
@@ -4864,7 +4864,7 @@
     <row r="146" ht="40" customHeight="1">
       <c r="A146" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FLAG_DIALOGUE.M-7.normal[3]</t>
+          <t xml:space="preserve">FLAG_DIALOGUE.M-7.standard[3]</t>
         </is>
       </c>
       <c r="B146" t="inlineStr" s="2">
@@ -4879,12 +4879,12 @@
       </c>
       <c r="D146" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">M-7.normal[3]</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">M-7.standard[3]</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G146" t="inlineStr" s="3">
@@ -5472,7 +5472,7 @@
     <row r="165" ht="40" customHeight="1">
       <c r="A165" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FLAG_DIALOGUE.M-8.normal[1]</t>
+          <t xml:space="preserve">FLAG_DIALOGUE.M-8.standard[1]</t>
         </is>
       </c>
       <c r="B165" t="inlineStr" s="2">
@@ -5487,12 +5487,12 @@
       </c>
       <c r="D165" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">M-8.normal[1]</t>
-        </is>
-      </c>
-      <c r="F165" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">M-8.standard[1]</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G165" t="inlineStr" s="3">
@@ -5504,7 +5504,7 @@
     <row r="166" ht="40" customHeight="1">
       <c r="A166" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FLAG_DIALOGUE.M-8.normal[2]</t>
+          <t xml:space="preserve">FLAG_DIALOGUE.M-8.standard[2]</t>
         </is>
       </c>
       <c r="B166" t="inlineStr" s="2">
@@ -5519,12 +5519,12 @@
       </c>
       <c r="D166" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">M-8.normal[2]</t>
-        </is>
-      </c>
-      <c r="F166" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">M-8.standard[2]</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G166" t="inlineStr" s="3">
@@ -5536,7 +5536,7 @@
     <row r="167" ht="40" customHeight="1">
       <c r="A167" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FLAG_DIALOGUE.M-8.normal[3]</t>
+          <t xml:space="preserve">FLAG_DIALOGUE.M-8.standard[3]</t>
         </is>
       </c>
       <c r="B167" t="inlineStr" s="2">
@@ -5551,12 +5551,12 @@
       </c>
       <c r="D167" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">M-8.normal[3]</t>
-        </is>
-      </c>
-      <c r="F167" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">M-8.standard[3]</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G167" t="inlineStr" s="3">
@@ -6144,7 +6144,7 @@
     <row r="186" ht="40" customHeight="1">
       <c r="A186" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FLAG_DIALOGUE.M-9.normal[1]</t>
+          <t xml:space="preserve">FLAG_DIALOGUE.M-9.standard[1]</t>
         </is>
       </c>
       <c r="B186" t="inlineStr" s="2">
@@ -6159,12 +6159,12 @@
       </c>
       <c r="D186" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">M-9.normal[1]</t>
-        </is>
-      </c>
-      <c r="F186" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">M-9.standard[1]</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G186" t="inlineStr" s="3">
@@ -6176,7 +6176,7 @@
     <row r="187" ht="40" customHeight="1">
       <c r="A187" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FLAG_DIALOGUE.M-9.normal[2]</t>
+          <t xml:space="preserve">FLAG_DIALOGUE.M-9.standard[2]</t>
         </is>
       </c>
       <c r="B187" t="inlineStr" s="2">
@@ -6191,12 +6191,12 @@
       </c>
       <c r="D187" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">M-9.normal[2]</t>
-        </is>
-      </c>
-      <c r="F187" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">M-9.standard[2]</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G187" t="inlineStr" s="3">
@@ -6208,7 +6208,7 @@
     <row r="188" ht="40" customHeight="1">
       <c r="A188" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FLAG_DIALOGUE.M-9.normal[3]</t>
+          <t xml:space="preserve">FLAG_DIALOGUE.M-9.standard[3]</t>
         </is>
       </c>
       <c r="B188" t="inlineStr" s="2">
@@ -6223,12 +6223,12 @@
       </c>
       <c r="D188" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">M-9.normal[3]</t>
-        </is>
-      </c>
-      <c r="F188" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">M-9.standard[3]</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G188" t="inlineStr" s="3">
@@ -6816,7 +6816,7 @@
     <row r="207" ht="40" customHeight="1">
       <c r="A207" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FLAG_DIALOGUE.M-10.normal[1]</t>
+          <t xml:space="preserve">FLAG_DIALOGUE.M-10.standard[1]</t>
         </is>
       </c>
       <c r="B207" t="inlineStr" s="2">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="D207" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">M-10.normal[1]</t>
-        </is>
-      </c>
-      <c r="F207" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">M-10.standard[1]</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G207" t="inlineStr" s="3">
@@ -6848,7 +6848,7 @@
     <row r="208" ht="40" customHeight="1">
       <c r="A208" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FLAG_DIALOGUE.M-10.normal[2]</t>
+          <t xml:space="preserve">FLAG_DIALOGUE.M-10.standard[2]</t>
         </is>
       </c>
       <c r="B208" t="inlineStr" s="2">
@@ -6863,12 +6863,12 @@
       </c>
       <c r="D208" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">M-10.normal[2]</t>
-        </is>
-      </c>
-      <c r="F208" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">M-10.standard[2]</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G208" t="inlineStr" s="3">
@@ -6880,7 +6880,7 @@
     <row r="209" ht="40" customHeight="1">
       <c r="A209" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FLAG_DIALOGUE.M-10.normal[3]</t>
+          <t xml:space="preserve">FLAG_DIALOGUE.M-10.standard[3]</t>
         </is>
       </c>
       <c r="B209" t="inlineStr" s="2">
@@ -6895,12 +6895,12 @@
       </c>
       <c r="D209" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">M-10.normal[3]</t>
-        </is>
-      </c>
-      <c r="F209" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">M-10.standard[3]</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G209" t="inlineStr" s="3">
@@ -7488,7 +7488,7 @@
     <row r="228" ht="40" customHeight="1">
       <c r="A228" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FLAG_DIALOGUE.M-11.normal[1]</t>
+          <t xml:space="preserve">FLAG_DIALOGUE.M-11.standard[1]</t>
         </is>
       </c>
       <c r="B228" t="inlineStr" s="2">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="D228" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">M-11.normal[1]</t>
-        </is>
-      </c>
-      <c r="F228" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">M-11.standard[1]</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G228" t="inlineStr" s="3">
@@ -7520,7 +7520,7 @@
     <row r="229" ht="40" customHeight="1">
       <c r="A229" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FLAG_DIALOGUE.M-11.normal[2]</t>
+          <t xml:space="preserve">FLAG_DIALOGUE.M-11.standard[2]</t>
         </is>
       </c>
       <c r="B229" t="inlineStr" s="2">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="D229" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">M-11.normal[2]</t>
-        </is>
-      </c>
-      <c r="F229" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">M-11.standard[2]</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G229" t="inlineStr" s="3">
@@ -7552,7 +7552,7 @@
     <row r="230" ht="40" customHeight="1">
       <c r="A230" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FLAG_DIALOGUE.M-11.normal[3]</t>
+          <t xml:space="preserve">FLAG_DIALOGUE.M-11.standard[3]</t>
         </is>
       </c>
       <c r="B230" t="inlineStr" s="2">
@@ -7567,12 +7567,12 @@
       </c>
       <c r="D230" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">M-11.normal[3]</t>
-        </is>
-      </c>
-      <c r="F230" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">M-11.standard[3]</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G230" t="inlineStr" s="3">
@@ -8160,7 +8160,7 @@
     <row r="249" ht="40" customHeight="1">
       <c r="A249" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FLAG_DIALOGUE.M-12.returner.normal[1]</t>
+          <t xml:space="preserve">FLAG_DIALOGUE.M-12.returner.standard[1]</t>
         </is>
       </c>
       <c r="B249" t="inlineStr" s="2">
@@ -8175,12 +8175,12 @@
       </c>
       <c r="D249" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">M-12.returner.normal[1]</t>
-        </is>
-      </c>
-      <c r="F249" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">M-12.returner.standard[1]</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G249" t="inlineStr" s="3">
@@ -8192,7 +8192,7 @@
     <row r="250" ht="40" customHeight="1">
       <c r="A250" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FLAG_DIALOGUE.M-12.returner.normal[2]</t>
+          <t xml:space="preserve">FLAG_DIALOGUE.M-12.returner.standard[2]</t>
         </is>
       </c>
       <c r="B250" t="inlineStr" s="2">
@@ -8207,12 +8207,12 @@
       </c>
       <c r="D250" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">M-12.returner.normal[2]</t>
-        </is>
-      </c>
-      <c r="F250" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">M-12.returner.standard[2]</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G250" t="inlineStr" s="3">
@@ -8224,7 +8224,7 @@
     <row r="251" ht="40" customHeight="1">
       <c r="A251" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FLAG_DIALOGUE.M-12.returner.normal[3]</t>
+          <t xml:space="preserve">FLAG_DIALOGUE.M-12.returner.standard[3]</t>
         </is>
       </c>
       <c r="B251" t="inlineStr" s="2">
@@ -8239,12 +8239,12 @@
       </c>
       <c r="D251" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">M-12.returner.normal[3]</t>
-        </is>
-      </c>
-      <c r="F251" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">M-12.returner.standard[3]</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G251" t="inlineStr" s="3">
@@ -8800,7 +8800,7 @@
     <row r="269" ht="40" customHeight="1">
       <c r="A269" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FLAG_DIALOGUE.M-12.forgiven.normal[1]</t>
+          <t xml:space="preserve">FLAG_DIALOGUE.M-12.forgiven.standard[1]</t>
         </is>
       </c>
       <c r="B269" t="inlineStr" s="2">
@@ -8815,12 +8815,12 @@
       </c>
       <c r="D269" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">M-12.forgiven.normal[1]</t>
-        </is>
-      </c>
-      <c r="F269" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">M-12.forgiven.standard[1]</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G269" t="inlineStr" s="3">
@@ -8832,7 +8832,7 @@
     <row r="270" ht="40" customHeight="1">
       <c r="A270" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FLAG_DIALOGUE.M-12.forgiven.normal[2]</t>
+          <t xml:space="preserve">FLAG_DIALOGUE.M-12.forgiven.standard[2]</t>
         </is>
       </c>
       <c r="B270" t="inlineStr" s="2">
@@ -8847,12 +8847,12 @@
       </c>
       <c r="D270" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">M-12.forgiven.normal[2]</t>
-        </is>
-      </c>
-      <c r="F270" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">M-12.forgiven.standard[2]</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G270" t="inlineStr" s="3">
@@ -8864,7 +8864,7 @@
     <row r="271" ht="40" customHeight="1">
       <c r="A271" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FLAG_DIALOGUE.M-12.forgiven.normal[3]</t>
+          <t xml:space="preserve">FLAG_DIALOGUE.M-12.forgiven.standard[3]</t>
         </is>
       </c>
       <c r="B271" t="inlineStr" s="2">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="D271" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">M-12.forgiven.normal[3]</t>
-        </is>
-      </c>
-      <c r="F271" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">M-12.forgiven.standard[3]</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G271" t="inlineStr" s="3">
@@ -9440,7 +9440,7 @@
     <row r="289" ht="40" customHeight="1">
       <c r="A289" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FLAG_DIALOGUE.M-12.notForgiven.normal[1]</t>
+          <t xml:space="preserve">FLAG_DIALOGUE.M-12.notForgiven.standard[1]</t>
         </is>
       </c>
       <c r="B289" t="inlineStr" s="2">
@@ -9455,12 +9455,12 @@
       </c>
       <c r="D289" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">M-12.notForgiven.normal[1]</t>
-        </is>
-      </c>
-      <c r="F289" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">M-12.notForgiven.standard[1]</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G289" t="inlineStr" s="3">
@@ -9472,7 +9472,7 @@
     <row r="290" ht="40" customHeight="1">
       <c r="A290" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FLAG_DIALOGUE.M-12.notForgiven.normal[2]</t>
+          <t xml:space="preserve">FLAG_DIALOGUE.M-12.notForgiven.standard[2]</t>
         </is>
       </c>
       <c r="B290" t="inlineStr" s="2">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="D290" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">M-12.notForgiven.normal[2]</t>
-        </is>
-      </c>
-      <c r="F290" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">M-12.notForgiven.standard[2]</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G290" t="inlineStr" s="3">
@@ -9504,7 +9504,7 @@
     <row r="291" ht="40" customHeight="1">
       <c r="A291" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FLAG_DIALOGUE.M-12.notForgiven.normal[3]</t>
+          <t xml:space="preserve">FLAG_DIALOGUE.M-12.notForgiven.standard[3]</t>
         </is>
       </c>
       <c r="B291" t="inlineStr" s="2">
@@ -9519,12 +9519,12 @@
       </c>
       <c r="D291" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">M-12.notForgiven.normal[3]</t>
-        </is>
-      </c>
-      <c r="F291" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">M-12.notForgiven.standard[3]</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G291" t="inlineStr" s="3">
@@ -10112,7 +10112,7 @@
     <row r="310" ht="40" customHeight="1">
       <c r="A310" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FLAG_DIALOGUE.M-13.master.normal[1]</t>
+          <t xml:space="preserve">FLAG_DIALOGUE.M-13.master.standard[1]</t>
         </is>
       </c>
       <c r="B310" t="inlineStr" s="2">
@@ -10127,12 +10127,12 @@
       </c>
       <c r="D310" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">M-13.master.normal[1]</t>
-        </is>
-      </c>
-      <c r="F310" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">M-13.master.standard[1]</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G310" t="inlineStr" s="3">
@@ -10144,7 +10144,7 @@
     <row r="311" ht="40" customHeight="1">
       <c r="A311" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FLAG_DIALOGUE.M-13.master.normal[2]</t>
+          <t xml:space="preserve">FLAG_DIALOGUE.M-13.master.standard[2]</t>
         </is>
       </c>
       <c r="B311" t="inlineStr" s="2">
@@ -10159,12 +10159,12 @@
       </c>
       <c r="D311" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">M-13.master.normal[2]</t>
-        </is>
-      </c>
-      <c r="F311" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">M-13.master.standard[2]</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G311" t="inlineStr" s="3">
@@ -10176,7 +10176,7 @@
     <row r="312" ht="40" customHeight="1">
       <c r="A312" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FLAG_DIALOGUE.M-13.master.normal[3]</t>
+          <t xml:space="preserve">FLAG_DIALOGUE.M-13.master.standard[3]</t>
         </is>
       </c>
       <c r="B312" t="inlineStr" s="2">
@@ -10191,12 +10191,12 @@
       </c>
       <c r="D312" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">M-13.master.normal[3]</t>
-        </is>
-      </c>
-      <c r="F312" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">M-13.master.standard[3]</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G312" t="inlineStr" s="3">
@@ -10784,7 +10784,7 @@
     <row r="331" ht="40" customHeight="1">
       <c r="A331" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FLAG_DIALOGUE.M-13.disciple.normal[1]</t>
+          <t xml:space="preserve">FLAG_DIALOGUE.M-13.disciple.standard[1]</t>
         </is>
       </c>
       <c r="B331" t="inlineStr" s="2">
@@ -10799,12 +10799,12 @@
       </c>
       <c r="D331" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">M-13.disciple.normal[1]</t>
-        </is>
-      </c>
-      <c r="F331" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">M-13.disciple.standard[1]</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G331" t="inlineStr" s="3">
@@ -10816,7 +10816,7 @@
     <row r="332" ht="40" customHeight="1">
       <c r="A332" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FLAG_DIALOGUE.M-13.disciple.normal[2]</t>
+          <t xml:space="preserve">FLAG_DIALOGUE.M-13.disciple.standard[2]</t>
         </is>
       </c>
       <c r="B332" t="inlineStr" s="2">
@@ -10831,12 +10831,12 @@
       </c>
       <c r="D332" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">M-13.disciple.normal[2]</t>
-        </is>
-      </c>
-      <c r="F332" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">M-13.disciple.standard[2]</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G332" t="inlineStr" s="3">
@@ -10848,7 +10848,7 @@
     <row r="333" ht="40" customHeight="1">
       <c r="A333" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FLAG_DIALOGUE.M-13.disciple.normal[3]</t>
+          <t xml:space="preserve">FLAG_DIALOGUE.M-13.disciple.standard[3]</t>
         </is>
       </c>
       <c r="B333" t="inlineStr" s="2">
@@ -10863,12 +10863,12 @@
       </c>
       <c r="D333" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">M-13.disciple.normal[3]</t>
-        </is>
-      </c>
-      <c r="F333" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">M-13.disciple.standard[3]</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G333" t="inlineStr" s="3">
@@ -11456,7 +11456,7 @@
     <row r="352" ht="40" customHeight="1">
       <c r="A352" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FLAG_DIALOGUE.M-14.normal[1]</t>
+          <t xml:space="preserve">FLAG_DIALOGUE.M-14.standard[1]</t>
         </is>
       </c>
       <c r="B352" t="inlineStr" s="2">
@@ -11471,12 +11471,12 @@
       </c>
       <c r="D352" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">M-14.normal[1]</t>
-        </is>
-      </c>
-      <c r="F352" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">M-14.standard[1]</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G352" t="inlineStr" s="3">
@@ -11488,7 +11488,7 @@
     <row r="353" ht="40" customHeight="1">
       <c r="A353" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FLAG_DIALOGUE.M-14.normal[2]</t>
+          <t xml:space="preserve">FLAG_DIALOGUE.M-14.standard[2]</t>
         </is>
       </c>
       <c r="B353" t="inlineStr" s="2">
@@ -11503,12 +11503,12 @@
       </c>
       <c r="D353" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">M-14.normal[2]</t>
-        </is>
-      </c>
-      <c r="F353" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">M-14.standard[2]</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G353" t="inlineStr" s="3">
@@ -11520,7 +11520,7 @@
     <row r="354" ht="40" customHeight="1">
       <c r="A354" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FLAG_DIALOGUE.M-14.normal[3]</t>
+          <t xml:space="preserve">FLAG_DIALOGUE.M-14.standard[3]</t>
         </is>
       </c>
       <c r="B354" t="inlineStr" s="2">
@@ -11535,12 +11535,12 @@
       </c>
       <c r="D354" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">M-14.normal[3]</t>
-        </is>
-      </c>
-      <c r="F354" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">M-14.standard[3]</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G354" t="inlineStr" s="3">
@@ -12128,7 +12128,7 @@
     <row r="373" ht="40" customHeight="1">
       <c r="A373" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FLAG_DIALOGUE.M-15.normal[1]</t>
+          <t xml:space="preserve">FLAG_DIALOGUE.M-15.standard[1]</t>
         </is>
       </c>
       <c r="B373" t="inlineStr" s="2">
@@ -12143,12 +12143,12 @@
       </c>
       <c r="D373" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">M-15.normal[1]</t>
-        </is>
-      </c>
-      <c r="F373" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">M-15.standard[1]</t>
+        </is>
+      </c>
+      <c r="E373" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G373" t="inlineStr" s="3">
@@ -12160,7 +12160,7 @@
     <row r="374" ht="40" customHeight="1">
       <c r="A374" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FLAG_DIALOGUE.M-15.normal[2]</t>
+          <t xml:space="preserve">FLAG_DIALOGUE.M-15.standard[2]</t>
         </is>
       </c>
       <c r="B374" t="inlineStr" s="2">
@@ -12175,12 +12175,12 @@
       </c>
       <c r="D374" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">M-15.normal[2]</t>
-        </is>
-      </c>
-      <c r="F374" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">M-15.standard[2]</t>
+        </is>
+      </c>
+      <c r="E374" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G374" t="inlineStr" s="3">
@@ -12192,7 +12192,7 @@
     <row r="375" ht="40" customHeight="1">
       <c r="A375" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FLAG_DIALOGUE.M-15.normal[3]</t>
+          <t xml:space="preserve">FLAG_DIALOGUE.M-15.standard[3]</t>
         </is>
       </c>
       <c r="B375" t="inlineStr" s="2">
@@ -12207,12 +12207,12 @@
       </c>
       <c r="D375" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">M-15.normal[3]</t>
-        </is>
-      </c>
-      <c r="F375" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">M-15.standard[3]</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G375" t="inlineStr" s="3">
@@ -12768,7 +12768,7 @@
     <row r="393" ht="40" customHeight="1">
       <c r="A393" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FLAG_DIALOGUE.M-16.normal[1]</t>
+          <t xml:space="preserve">FLAG_DIALOGUE.M-16.standard[1]</t>
         </is>
       </c>
       <c r="B393" t="inlineStr" s="2">
@@ -12783,12 +12783,12 @@
       </c>
       <c r="D393" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">M-16.normal[1]</t>
-        </is>
-      </c>
-      <c r="F393" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">M-16.standard[1]</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G393" t="inlineStr" s="3">
@@ -12800,7 +12800,7 @@
     <row r="394" ht="40" customHeight="1">
       <c r="A394" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FLAG_DIALOGUE.M-16.normal[2]</t>
+          <t xml:space="preserve">FLAG_DIALOGUE.M-16.standard[2]</t>
         </is>
       </c>
       <c r="B394" t="inlineStr" s="2">
@@ -12815,12 +12815,12 @@
       </c>
       <c r="D394" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">M-16.normal[2]</t>
-        </is>
-      </c>
-      <c r="F394" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">M-16.standard[2]</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G394" t="inlineStr" s="3">
@@ -12832,7 +12832,7 @@
     <row r="395" ht="40" customHeight="1">
       <c r="A395" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FLAG_DIALOGUE.M-16.normal[3]</t>
+          <t xml:space="preserve">FLAG_DIALOGUE.M-16.standard[3]</t>
         </is>
       </c>
       <c r="B395" t="inlineStr" s="2">
@@ -12847,12 +12847,12 @@
       </c>
       <c r="D395" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">M-16.normal[3]</t>
-        </is>
-      </c>
-      <c r="F395" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">M-16.standard[3]</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G395" t="inlineStr" s="3">
@@ -13408,7 +13408,7 @@
     <row r="413" ht="40" customHeight="1">
       <c r="A413" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FLAG_DIALOGUE.M-17.normal[1]</t>
+          <t xml:space="preserve">FLAG_DIALOGUE.M-17.standard[1]</t>
         </is>
       </c>
       <c r="B413" t="inlineStr" s="2">
@@ -13423,12 +13423,12 @@
       </c>
       <c r="D413" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">M-17.normal[1]</t>
-        </is>
-      </c>
-      <c r="F413" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">M-17.standard[1]</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G413" t="inlineStr" s="3">
@@ -13440,7 +13440,7 @@
     <row r="414" ht="40" customHeight="1">
       <c r="A414" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FLAG_DIALOGUE.M-17.normal[2]</t>
+          <t xml:space="preserve">FLAG_DIALOGUE.M-17.standard[2]</t>
         </is>
       </c>
       <c r="B414" t="inlineStr" s="2">
@@ -13455,12 +13455,12 @@
       </c>
       <c r="D414" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">M-17.normal[2]</t>
-        </is>
-      </c>
-      <c r="F414" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">M-17.standard[2]</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G414" t="inlineStr" s="3">
@@ -13472,7 +13472,7 @@
     <row r="415" ht="40" customHeight="1">
       <c r="A415" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FLAG_DIALOGUE.M-17.normal[3]</t>
+          <t xml:space="preserve">FLAG_DIALOGUE.M-17.standard[3]</t>
         </is>
       </c>
       <c r="B415" t="inlineStr" s="2">
@@ -13487,12 +13487,12 @@
       </c>
       <c r="D415" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">M-17.normal[3]</t>
-        </is>
-      </c>
-      <c r="F415" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">M-17.standard[3]</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G415" t="inlineStr" s="3">
@@ -14048,7 +14048,7 @@
     <row r="433" ht="40" customHeight="1">
       <c r="A433" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FLAG_DIALOGUE.M-18.normal[1]</t>
+          <t xml:space="preserve">FLAG_DIALOGUE.M-18.standard[1]</t>
         </is>
       </c>
       <c r="B433" t="inlineStr" s="2">
@@ -14063,12 +14063,12 @@
       </c>
       <c r="D433" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">M-18.normal[1]</t>
-        </is>
-      </c>
-      <c r="F433" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">M-18.standard[1]</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G433" t="inlineStr" s="3">
@@ -14080,7 +14080,7 @@
     <row r="434" ht="40" customHeight="1">
       <c r="A434" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FLAG_DIALOGUE.M-18.normal[2]</t>
+          <t xml:space="preserve">FLAG_DIALOGUE.M-18.standard[2]</t>
         </is>
       </c>
       <c r="B434" t="inlineStr" s="2">
@@ -14095,12 +14095,12 @@
       </c>
       <c r="D434" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">M-18.normal[2]</t>
-        </is>
-      </c>
-      <c r="F434" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">M-18.standard[2]</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G434" t="inlineStr" s="3">
@@ -14112,7 +14112,7 @@
     <row r="435" ht="40" customHeight="1">
       <c r="A435" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FLAG_DIALOGUE.M-18.normal[3]</t>
+          <t xml:space="preserve">FLAG_DIALOGUE.M-18.standard[3]</t>
         </is>
       </c>
       <c r="B435" t="inlineStr" s="2">
@@ -14127,12 +14127,12 @@
       </c>
       <c r="D435" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">M-18.normal[3]</t>
-        </is>
-      </c>
-      <c r="F435" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">M-18.standard[3]</t>
+        </is>
+      </c>
+      <c r="E435" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G435" t="inlineStr" s="3">

--- a/セリフ編集/その他セリフ/17-関係性フラグ.xlsx
+++ b/セリフ編集/その他セリフ/17-関係性フラグ.xlsx
@@ -14144,7 +14144,7 @@
     <row r="436" ht="40" customHeight="1">
       <c r="A436" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FLAG_DIALOGUE.M-19.normal[1]</t>
+          <t xml:space="preserve">FLAG_DIALOGUE.M-19.standard[1]</t>
         </is>
       </c>
       <c r="B436" t="inlineStr" s="2">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="D436" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">M-19.normal[1]</t>
-        </is>
-      </c>
-      <c r="F436" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">M-19.standard[1]</t>
+        </is>
+      </c>
+      <c r="E436" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G436" t="inlineStr" s="3">
@@ -14176,7 +14176,7 @@
     <row r="437" ht="40" customHeight="1">
       <c r="A437" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FLAG_DIALOGUE.M-19.normal[2]</t>
+          <t xml:space="preserve">FLAG_DIALOGUE.M-19.standard[2]</t>
         </is>
       </c>
       <c r="B437" t="inlineStr" s="2">
@@ -14191,12 +14191,12 @@
       </c>
       <c r="D437" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">M-19.normal[2]</t>
-        </is>
-      </c>
-      <c r="F437" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">M-19.standard[2]</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G437" t="inlineStr" s="3">
@@ -14208,7 +14208,7 @@
     <row r="438" ht="40" customHeight="1">
       <c r="A438" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FLAG_DIALOGUE.M-19.normal[3]</t>
+          <t xml:space="preserve">FLAG_DIALOGUE.M-19.standard[3]</t>
         </is>
       </c>
       <c r="B438" t="inlineStr" s="2">
@@ -14223,12 +14223,12 @@
       </c>
       <c r="D438" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">M-19.normal[3]</t>
-        </is>
-      </c>
-      <c r="F438" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">M-19.standard[3]</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G438" t="inlineStr" s="3">
@@ -14240,7 +14240,7 @@
     <row r="439" ht="40" customHeight="1">
       <c r="A439" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FLAG_DIALOGUE.M-20.normal[1]</t>
+          <t xml:space="preserve">FLAG_DIALOGUE.M-20.standard[1]</t>
         </is>
       </c>
       <c r="B439" t="inlineStr" s="2">
@@ -14255,12 +14255,12 @@
       </c>
       <c r="D439" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">M-20.normal[1]</t>
-        </is>
-      </c>
-      <c r="F439" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">M-20.standard[1]</t>
+        </is>
+      </c>
+      <c r="E439" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G439" t="inlineStr" s="3">
@@ -14272,7 +14272,7 @@
     <row r="440" ht="40" customHeight="1">
       <c r="A440" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FLAG_DIALOGUE.M-20.normal[2]</t>
+          <t xml:space="preserve">FLAG_DIALOGUE.M-20.standard[2]</t>
         </is>
       </c>
       <c r="B440" t="inlineStr" s="2">
@@ -14287,12 +14287,12 @@
       </c>
       <c r="D440" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">M-20.normal[2]</t>
-        </is>
-      </c>
-      <c r="F440" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">M-20.standard[2]</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G440" t="inlineStr" s="3">
@@ -14304,7 +14304,7 @@
     <row r="441" ht="40" customHeight="1">
       <c r="A441" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FLAG_DIALOGUE.M-20.normal[3]</t>
+          <t xml:space="preserve">FLAG_DIALOGUE.M-20.standard[3]</t>
         </is>
       </c>
       <c r="B441" t="inlineStr" s="2">
@@ -14319,12 +14319,12 @@
       </c>
       <c r="D441" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">M-20.normal[3]</t>
-        </is>
-      </c>
-      <c r="F441" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">M-20.standard[3]</t>
+        </is>
+      </c>
+      <c r="E441" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G441" t="inlineStr" s="3">
@@ -14336,7 +14336,7 @@
     <row r="442" ht="40" customHeight="1">
       <c r="A442" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FLAG_DIALOGUE.M-21.normal[1]</t>
+          <t xml:space="preserve">FLAG_DIALOGUE.M-21.standard[1]</t>
         </is>
       </c>
       <c r="B442" t="inlineStr" s="2">
@@ -14351,12 +14351,12 @@
       </c>
       <c r="D442" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">M-21.normal[1]</t>
-        </is>
-      </c>
-      <c r="F442" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">M-21.standard[1]</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G442" t="inlineStr" s="3">
@@ -14368,7 +14368,7 @@
     <row r="443" ht="40" customHeight="1">
       <c r="A443" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FLAG_DIALOGUE.M-21.normal[2]</t>
+          <t xml:space="preserve">FLAG_DIALOGUE.M-21.standard[2]</t>
         </is>
       </c>
       <c r="B443" t="inlineStr" s="2">
@@ -14383,12 +14383,12 @@
       </c>
       <c r="D443" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">M-21.normal[2]</t>
-        </is>
-      </c>
-      <c r="F443" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">M-21.standard[2]</t>
+        </is>
+      </c>
+      <c r="E443" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G443" t="inlineStr" s="3">
@@ -14400,7 +14400,7 @@
     <row r="444" ht="40" customHeight="1">
       <c r="A444" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FLAG_DIALOGUE.M-21.normal[3]</t>
+          <t xml:space="preserve">FLAG_DIALOGUE.M-21.standard[3]</t>
         </is>
       </c>
       <c r="B444" t="inlineStr" s="2">
@@ -14415,12 +14415,12 @@
       </c>
       <c r="D444" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">M-21.normal[3]</t>
-        </is>
-      </c>
-      <c r="F444" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">M-21.standard[3]</t>
+        </is>
+      </c>
+      <c r="E444" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G444" t="inlineStr" s="3">
@@ -14432,7 +14432,7 @@
     <row r="445" ht="40" customHeight="1">
       <c r="A445" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FLAG_DIALOGUE.M-22.normal[1]</t>
+          <t xml:space="preserve">FLAG_DIALOGUE.M-22.standard[1]</t>
         </is>
       </c>
       <c r="B445" t="inlineStr" s="2">
@@ -14447,12 +14447,12 @@
       </c>
       <c r="D445" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">M-22.normal[1]</t>
-        </is>
-      </c>
-      <c r="F445" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">M-22.standard[1]</t>
+        </is>
+      </c>
+      <c r="E445" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G445" t="inlineStr" s="3">
@@ -14464,7 +14464,7 @@
     <row r="446" ht="40" customHeight="1">
       <c r="A446" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FLAG_DIALOGUE.M-22.normal[2]</t>
+          <t xml:space="preserve">FLAG_DIALOGUE.M-22.standard[2]</t>
         </is>
       </c>
       <c r="B446" t="inlineStr" s="2">
@@ -14479,12 +14479,12 @@
       </c>
       <c r="D446" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">M-22.normal[2]</t>
-        </is>
-      </c>
-      <c r="F446" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">M-22.standard[2]</t>
+        </is>
+      </c>
+      <c r="E446" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G446" t="inlineStr" s="3">
@@ -14496,7 +14496,7 @@
     <row r="447" ht="40" customHeight="1">
       <c r="A447" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FLAG_DIALOGUE.M-22.normal[3]</t>
+          <t xml:space="preserve">FLAG_DIALOGUE.M-22.standard[3]</t>
         </is>
       </c>
       <c r="B447" t="inlineStr" s="2">
@@ -14511,12 +14511,12 @@
       </c>
       <c r="D447" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">M-22.normal[3]</t>
-        </is>
-      </c>
-      <c r="F447" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">M-22.standard[3]</t>
+        </is>
+      </c>
+      <c r="E447" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G447" t="inlineStr" s="3">
@@ -14528,7 +14528,7 @@
     <row r="448" ht="40" customHeight="1">
       <c r="A448" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FLAG_DIALOGUE.M-23.normal[1]</t>
+          <t xml:space="preserve">FLAG_DIALOGUE.M-23.standard[1]</t>
         </is>
       </c>
       <c r="B448" t="inlineStr" s="2">
@@ -14543,12 +14543,12 @@
       </c>
       <c r="D448" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">M-23.normal[1]</t>
-        </is>
-      </c>
-      <c r="F448" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">M-23.standard[1]</t>
+        </is>
+      </c>
+      <c r="E448" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G448" t="inlineStr" s="3">
@@ -14560,7 +14560,7 @@
     <row r="449" ht="40" customHeight="1">
       <c r="A449" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FLAG_DIALOGUE.M-23.normal[2]</t>
+          <t xml:space="preserve">FLAG_DIALOGUE.M-23.standard[2]</t>
         </is>
       </c>
       <c r="B449" t="inlineStr" s="2">
@@ -14575,12 +14575,12 @@
       </c>
       <c r="D449" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">M-23.normal[2]</t>
-        </is>
-      </c>
-      <c r="F449" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">M-23.standard[2]</t>
+        </is>
+      </c>
+      <c r="E449" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G449" t="inlineStr" s="3">
@@ -14592,7 +14592,7 @@
     <row r="450" ht="40" customHeight="1">
       <c r="A450" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FLAG_DIALOGUE.M-23.normal[3]</t>
+          <t xml:space="preserve">FLAG_DIALOGUE.M-23.standard[3]</t>
         </is>
       </c>
       <c r="B450" t="inlineStr" s="2">
@@ -14607,12 +14607,12 @@
       </c>
       <c r="D450" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">M-23.normal[3]</t>
-        </is>
-      </c>
-      <c r="F450" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">M-23.standard[3]</t>
+        </is>
+      </c>
+      <c r="E450" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G450" t="inlineStr" s="3">
